--- a/光伏配储项目/电价数据/2026/长沙站.xlsx
+++ b/光伏配储项目/电价数据/2026/长沙站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.41803</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7965599999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.46208</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.48379</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.03185</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.2467</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.15558</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.01616</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.04709000000000001</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.09706000000000001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.10097</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.08642</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.0366</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.52585</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.56286</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7439</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14877</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.40616</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66887</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.89579</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5059</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.2192</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.35415</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.16872</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.05275</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31613</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41876</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45825</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.71108</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.76313</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.14441</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95482</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.91401</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8089700000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7716000000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5206499999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49163</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43207</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73526</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.91199</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9787100000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51524</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5426599999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.52274</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50405</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40879</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48437</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.49139</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.46038</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.45252</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.36045</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.34395</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.53285</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.54192</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.39765</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49369</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.00479</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.01037</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.20042</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01149</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.14498</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5611699999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2109</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.02098</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.01965</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.43043</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.60825</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.77738</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8130499999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.19667</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.44525</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.14759</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86982</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.23591</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.13165</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.28075</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03431</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.11597</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.67384</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00942</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.93133</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.98814</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.83029</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8617100000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.72536</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45598</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.6982</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.73786</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45543</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44947</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33557</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52411</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50266</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5029399999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37497</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45423</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48872</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45199</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.04055</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.23186</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.03382</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.02719</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.03983</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.02221</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80544</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.12389</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.47061</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.33481</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63101</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6719700000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50776</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.42828</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.52346</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6192300000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44069</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.51287</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6327200000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.5415800000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55947</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7271799999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.59429</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.49583</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.51555</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46199</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34299</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5240900000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51093</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44544</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45937</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.02157</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.02814</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.02902</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.03845000000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59626</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21742</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.19036</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6427200000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.07479000000000001</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.05152</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.08685</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.21297</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47657</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52771</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45112</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47489</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.09193999999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.2103</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.53189</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.52418</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49606</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5045299999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33149</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.03885</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.08434</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03612</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13283</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03035</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03482</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.07792</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.04593999999999999</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41039</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.28485</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.005860000000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.20456</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.04392</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.07828</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.04694</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2196</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.25899</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.009800000000000001</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.14622</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.16975</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.0994</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.06833</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.03196</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.27661</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.16315</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.19435</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.06573000000000001</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.22021</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00587</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19831</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14075</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01057</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05245</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05063</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.29691</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33512</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46061</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78574</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86974</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61378</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.55621</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42034</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.23093</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.24654</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.21368</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5073299999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.48877</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.89151</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47657</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.16606</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83129</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.20251</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.02876</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.27863</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.1182</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6014299999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.41118</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.25636</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.04901</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.21658</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.21112</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.23314</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.20209</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.23917</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.27945</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.27174</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.25197</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.25252</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.19885</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.19685</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.17098</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.19505</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.22245</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.20864</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.29476</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.85661</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.25709</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.22417</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.26212</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.19421</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.24635</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.22067</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.24236</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.25734</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.25876</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.27058</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.19256</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.25397</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.20971</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.25296</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.24142</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.24526</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.26076</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.26661</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.09868</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.25994</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.04448</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25316</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.14002</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26069</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20412</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.07033</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.26511</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28547</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.24662</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.26035</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.26529</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.17644</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.26363</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.2288</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.21752</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.02257</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.11312</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.66912</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44688</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16693</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.67363</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.76747</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6234700000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.01168</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41186</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46408</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.15745</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.19327</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.15955</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.14247</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.15956</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.18837</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.17953</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.00146</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.24887</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.1979</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.25115</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.13574</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.25182</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.04726</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26555</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27695</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.26634</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.21198</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.2124</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.19396</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.24766</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.25706</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.25078</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.20591</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.19357</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.12764</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.17747</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.16306</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.27606</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.05479999999999999</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.05155</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.04172</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-0.01154</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.16062</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.18525</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.18213</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.26248</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.00538</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.006059999999999999</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.06082</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>-0.00826</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.06629</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.00085</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>-0.005589999999999999</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.19096</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.13718</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.21562</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>-0.01124</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.26181</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.26546</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.00032</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.11717</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.03734000000000001</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.03388</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.03818999999999999</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.02167</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.00274</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.20043</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.01844</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25928</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.03507</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.04501</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.00513</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.24746</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.20969</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.24539</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.22428</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.24447</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.21193</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.18296</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.25662</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.23003</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.26001</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.21711</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.22705</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.20975</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.14786</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.19519</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.21083</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.1928</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.20495</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.16385</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.15606</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.16412</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.21265</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.21672</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.15511</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.21674</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.24198</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.09415000000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.15813</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.19782</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.20179</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.23015</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.22395</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.22717</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.22216</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.22701</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.24049</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.21886</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.24383</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.24605</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.24783</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.25263</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.15828</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.22403</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.2244</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.24224</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.24348</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.26267</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.26373</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.26858</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.26728</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.26055</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23586</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25869</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18367</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14323</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.25731</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.17935</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.05470000000000001</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21691</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.2426</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.27895</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24294</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.24275</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.19264</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.1357</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.25359</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.12275</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.16438</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.26285</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.28347</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.27035</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.19875</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.24087</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.23872</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.252</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.25206</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.09875</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.12205</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.24465</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.25699</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.20801</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.22805</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.22369</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.24145</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.25096</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.25094</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.24076</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.24928</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.25003</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.24958</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.24345</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.20126</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.23808</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.25107</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.25762</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.08109</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.62691</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.46662</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26769</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27057</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17556</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-0.00186</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5541200000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.25745</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.55303</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.65992</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>-0.00125</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.08387</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.44918</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.19397</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.27285</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.26147</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.20364</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.21713</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.06642000000000001</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.21739</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.14936</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.22069</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.22409</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.21296</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.19091</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.05675</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.05294</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.21496</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.21291</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.21994</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.21953</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.22074</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.22291</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.05368</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.05377000000000001</v>
+      </c>
+      <c r="U130" t="n">
+        <v>-0.01306</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.15259</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.26119</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.26436</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.06031</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.09715</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.05881</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>-0.01108</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>-0.01286</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.08384999999999999</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.14595</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.2404</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.22045</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.25672</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.22569</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.24622</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.24755</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.25767</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.2493</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.22418</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.24869</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.26913</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.26663</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.27483</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.23963</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.24109</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.21755</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.23737</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.24581</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.07906000000000001</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.24097</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.17815</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.24139</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.24961</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.06609999999999999</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.23061</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.12584</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.20416</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.18535</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.20347</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.18018</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.19303</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.07404999999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.17667</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.06872</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-0.01119</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.11997</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.28996</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.24559</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.21231</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.28963</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.23012</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.22175</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.21056</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.23179</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.19738</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.26462</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.22786</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.21802</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.28528</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.23265</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.23023</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.22924</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.22091</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.22012</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.24544</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.21649</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.23233</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.25641</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.27316</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.23558</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.25919</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.23177</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.59523</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.03355</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.04837</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.20217</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.20305</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.24906</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.26467</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.19799</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.23902</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.23049</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25068</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.03594</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.08170999999999999</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.00263</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20506</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21455</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20127</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27183</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25044</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26241</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.26623</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.27619</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.24862</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.15681</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.26118</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.61439</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.57212</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60373</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.10585</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7781699999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.14829</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.05594</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45874</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.19046</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.13504</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.20772</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.21786</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.27007</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.17556</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.11707</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.15081</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.22687</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.22357</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.23979</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.22525</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.2456</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.25963</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.26308</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.20562</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.23342</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.20636</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.23105</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.20988</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.21234</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.19337</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.11906</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.15003</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.03934</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.17709</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.18029</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.39769</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.49691</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.25534</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.00676</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.20971</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40666</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6578200000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7205</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.04631</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.19876</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.01162</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.23204</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.27943</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.00753</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.04377</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.04652000000000001</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.05317</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.02623</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.05822</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.21712</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.16912</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.18026</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.13832</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.13206</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.09981999999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>-0.04702000000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>-0.03242</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>-0.02066</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.70927</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.56335</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.61364</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.13115</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.13456</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.15765</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.17107</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.16711</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.23022</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.11146</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.21812</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.20427</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.18512</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.22958</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.08337</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.17974</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.18107</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.23216</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.23254</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.25187</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.23871</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.18328</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.20996</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.16882</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.17915</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-0.01222</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.01267</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.01031</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.00627</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21796</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.0262</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.20326</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.07723000000000001</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.02611</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.04194</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.04065</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.1676</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.06745</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.12794</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.10157</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.24651</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.24809</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.20451</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.08394</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.09718</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.07659000000000001</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.06434999999999999</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.09057999999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.15496</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.18958</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.10142</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.16242</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.21637</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.18393</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.00313</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.02398</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.0008100000000000001</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.00481</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.05442</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.12062</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.08359</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.13881</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.07451000000000001</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.09991</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.06593</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.16936</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-0.01061</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.05825</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="R135" t="n">
+        <v>-0.01217</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>-0.01311</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.01259</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.05594</v>
+      </c>
+      <c r="W135" t="n">
+        <v>-0.01272</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-0.01224</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>-0.01176</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>-0.01127</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.04988</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.01051</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.0161</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.01338</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.01752</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.02723</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.01418</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.02933</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03969</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.02048</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.20722</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.02293</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.04097</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.02509</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.26314</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.01578</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16295</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.03022</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.02273</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.02681</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.01895</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.03515</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.24389</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.23959</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.24277</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.25791</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.23973</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.25823</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.13698</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.18014</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.19591</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.20791</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.22877</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.25646</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.14627</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.20445</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.16767</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.17533</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.06852</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.09506999999999999</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.07188</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.11749</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.15574</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.20258</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.16855</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.14622</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>-0.00868</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>-0.00583</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.16628</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>-0.01069</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.21007</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>-0.009179999999999999</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.12361</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.13874</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.18714</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.22225</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.21752</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.22245</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.20812</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.04941</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.04828</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.21823</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.09984</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.13683</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.12322</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.09337999999999999</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21711</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.03127</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00088</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15601</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02272</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0143</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02946</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03823</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00264</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03562</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01157</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03528</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20792</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27021</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.25357</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26433</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.24552</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.27062</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.25664</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.24329</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23399</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.26221</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.19197</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.28201</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.25161</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.26383</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.25635</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.23959</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27153</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.19316</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.19286</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.13919</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.17014</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.11559</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.18069</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-0.01769</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.01069</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-0.009689999999999999</v>
+      </c>
+      <c r="O137" t="n">
+        <v>-0.01009</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>-0.01122</v>
+      </c>
+      <c r="R137" t="n">
+        <v>-0.01302</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>-0.00571</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.19804</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.07607999999999999</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.83308</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8716799999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03845000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16612</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00241</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.04702000000000001</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04499</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.26716</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.26128</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.24559</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.21463</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.92115</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.04305</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.78351</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.78176</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.78588</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8823</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.03897999999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.24112</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.24096</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.17585</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.01555</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44085</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.12178</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.15726</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.12515</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-0.00709</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.17073</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.15414</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.09040999999999999</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.05931</v>
+      </c>
+      <c r="T138" t="n">
+        <v>-0.01122</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.05714</v>
+      </c>
+      <c r="V138" t="n">
+        <v>-0.01228</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-0.01159</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>-0.008330000000000001</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.07156999999999999</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.13355</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.05332</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.09068999999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.16765</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.08056999999999999</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>-5.999999999999999e-05</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.2322</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.15337</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.12058</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04853</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.10604</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25982</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.27065</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.14049</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.20375</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>-0.00205</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.18593</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.18366</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.21538</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.11135</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.25517</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.23411</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.23077</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.21555</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.22245</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.27188</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24215</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.25756</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.25675</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.26197</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.27242</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.25789</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.25454</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.26746</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.25424</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.25086</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.25132</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.24112</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.24761</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.25101</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.25138</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.25135</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.25335</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.25183</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.25407</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.26439</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.26558</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.15364</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.24109</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.24701</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.09082</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.1373</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.25276</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40416</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7649900000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.54604</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.20742</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.49162</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.83033</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.23112</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.10452</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.18396</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.17186</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.20074</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.11936</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.24296</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.21075</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.25486</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.26035</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.1501</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.26488</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.25342</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.26322</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.28895</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.24779</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.24948</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.25627</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.25149</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.26055</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.26784</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.26874</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.27008</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.26962</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.25108</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.24786</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.24586</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.23646</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.21368</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.22931</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45352</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.7397100000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.55479</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.8135599999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7305</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.57136</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.20083</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.26964</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25939</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.22096</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.23289</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.2271</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.25022</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.24216</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.2153</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.24475</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.25076</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.23362</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.23217</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.21865</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.21174</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.19918</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.25241</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25199</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.14937</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>-0.04311</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.22927</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.15349</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.16226</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23433</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.24555</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03202</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.17704</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27754</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.03246</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01908</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.18146</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.19706</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03632</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05899</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23666</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25327</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.21817</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.20915</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.11428</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.01082</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.12511</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.16623</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.21578</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42596</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.08091</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.09067</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.07993</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.07401000000000001</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.26684</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.18663</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.14696</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.26847</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.02569</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.17252</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.18126</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.05597</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.08476</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.08445</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.13165</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.10577</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.04789</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.11573</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.17488</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.17986</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.07493999999999999</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.15436</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.17385</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.20951</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.18804</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.18693</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.12825</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.18268</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.18336</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.18832</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.18222</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.16615</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.18265</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.18186</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.19887</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.17874</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.14897</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.18643</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.17972</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.17902</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.2169</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.21416</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.17554</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.17455</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.18047</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.22079</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2285</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.23359</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23925</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.11983</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.28214</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.24283</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43716</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.22099</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.20389</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.20495</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.18502</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.22628</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.14402</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.29167</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.22239</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.22741</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42365</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.21656</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.19855</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.21264</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.1977</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.20707</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.21039</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.20311</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.24952</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.23975</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.23207</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.17379</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.16453</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.17292</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.17464</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.20162</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.24341</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.08141</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.13661</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.15435</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.16476</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.16893</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.2018</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.18807</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.18829</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.16353</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.18042</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.20278</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.19042</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.25963</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17676</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1464</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19959</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04757</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04772999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13439</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00051</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17771</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22779</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27091</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15796</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24169</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22115</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00326</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20211</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15161</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26442</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27679</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47751</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40572</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.14646</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.18375</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.13438</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.23402</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.26096</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.18896</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.25773</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.25426</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.26544</v>
       </c>
     </row>
   </sheetData>
